--- a/data/trans_camb/P44D-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P44D-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-16,16</t>
+          <t>-15,36</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-20,65</t>
+          <t>-21,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-17,97</t>
+          <t>-17,62</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 27,79</t>
+          <t>-38,82; 23,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 6,45</t>
+          <t>-42,9; 8,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 46,18</t>
+          <t>-37,51; 46,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 6,91</t>
+          <t>-47,19; 8,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 23,04</t>
+          <t>-27,38; 21,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 1,44</t>
+          <t>-37,57; 1,51</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-42,69%</t>
+          <t>-40,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-48,16%</t>
+          <t>-49,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-45,08%</t>
+          <t>-44,2%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 179,16</t>
+          <t>-66,14; 166,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,82; 31,81</t>
+          <t>-70,17; 47,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,31; 214,74</t>
+          <t>-68,08; 221,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 47,8</t>
+          <t>-71,43; 46,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,07; 102,61</t>
+          <t>-54,0; 90,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,81; 3,5</t>
+          <t>-64,63; 7,58</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-22,63</t>
+          <t>-21,67</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-25,51</t>
+          <t>-26,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-23,66</t>
+          <t>-23,54</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 23,12</t>
+          <t>-39,97; 24,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 5,07</t>
+          <t>-50,05; 2,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-63,79; 48,88</t>
+          <t>-69,0; 49,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 14,21</t>
+          <t>-74,7; 11,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 17,62</t>
+          <t>-38,2; 18,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,54; -1,17</t>
+          <t>-46,53; -1,18</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-57,0%</t>
+          <t>-54,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-62,59%</t>
+          <t>-65,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-59,07%</t>
+          <t>-58,79%</t>
         </is>
       </c>
     </row>
@@ -863,12 +863,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,32; 153,83</t>
+          <t>-69,17; 183,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-80,53; 44,02</t>
+          <t>-78,62; 28,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,71; —</t>
+          <t>-89,29; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 97,92</t>
+          <t>-68,47; 113,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,31; -5,03</t>
+          <t>-77,56; -5,08</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-30,97</t>
+          <t>-29,46</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,06</t>
+          <t>-5,71</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 21,97</t>
+          <t>-4,15; 22,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 4,8</t>
+          <t>-9,3; 8,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-72,96; -8,59</t>
+          <t>-73,25; -8,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-68,45; -2,8</t>
+          <t>-68,82; -3,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 9,42</t>
+          <t>-20,64; 9,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,65; -0,38</t>
+          <t>-20,91; 3,75</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-48,95%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-87,99%</t>
+          <t>-83,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-83,82%</t>
+          <t>-47,62%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -11,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 300,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-99,02; -25,43</t>
+          <t>-87,8; 128,18</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,77</t>
+          <t>0,0; 13,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,98</t>
+          <t>0,4; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,98</t>
+          <t>0,0; 26,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,85</t>
+          <t>1,92; 8,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,35</t>
+          <t>1,39; 13,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,79</t>
+          <t>1,42; 5,41</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-11,02</t>
+          <t>-11,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,17</t>
+          <t>-8,19</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 0,0</t>
+          <t>-35,79; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 0,34</t>
+          <t>-35,52; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 0,0</t>
+          <t>-27,04; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 0,0</t>
+          <t>-27,72; 0,0</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-96,9%</t>
+          <t>-97,11%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-97,39%</t>
+          <t>-97,58%</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-4,53</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>-4,64</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 19,76</t>
+          <t>-13,9; 19,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 3,66</t>
+          <t>-24,81; 3,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 19,76</t>
+          <t>-13,9; 19,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 3,56</t>
+          <t>-24,33; 3,48</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-50,51%</t>
+          <t>-52,34%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-52,05%</t>
+          <t>-53,68%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-91,08; —</t>
+          <t>-92,22; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-93,87; —</t>
+          <t>-93,7; —</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-6,36</t>
+          <t>-3,17</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-9,78</t>
+          <t>-9,85</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,12</t>
+          <t>-6,42</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 9,68</t>
+          <t>-9,35; 9,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 0,58</t>
+          <t>-13,49; 3,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 4,32</t>
+          <t>-16,2; 4,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-20,09; -2,69</t>
+          <t>-19,49; -2,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 4,66</t>
+          <t>-9,42; 4,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -2,82</t>
+          <t>-13,0; -1,5</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-48,96%</t>
+          <t>-24,42%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-56,96%</t>
+          <t>-57,39%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-53,98%</t>
+          <t>-42,66%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 125,34</t>
+          <t>-52,31; 128,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 0,72</t>
+          <t>-61,16; 54,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-67,9; 43,78</t>
+          <t>-70,7; 59,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-74,93; -24,87</t>
+          <t>-74,7; -23,66</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 44,69</t>
+          <t>-47,09; 40,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-77,29; -29,36</t>
+          <t>-61,56; -12,57</t>
         </is>
       </c>
     </row>
